--- a/skills/draft-legal-docs/templates/证据目录.template.xlsx
+++ b/skills/draft-legal-docs/templates/证据目录.template.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>证  据  目  录</t>
   </si>
@@ -59,28 +59,22 @@
     <t>【本组证据证明内容简述】</t>
   </si>
   <si>
-    <t>1-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">二 </t>
+    <t>二</t>
+  </si>
+  <si>
+    <t>三</t>
   </si>
   <si>
     <t>【证据大类型名称】</t>
   </si>
   <si>
-    <t>8-11</t>
-  </si>
-  <si>
-    <t>三</t>
-  </si>
-  <si>
-    <t>12-54</t>
-  </si>
-  <si>
     <t>四</t>
   </si>
   <si>
-    <t>55-154</t>
+    <t>五</t>
+  </si>
+  <si>
+    <t>六</t>
   </si>
   <si>
     <t>目录制作日期：YY-MM-DD</t>
@@ -734,7 +728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -754,13 +748,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1348,28 +1345,26 @@
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
+      <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5">
-        <v>2</v>
-      </c>
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5"/>
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:5">
@@ -1383,78 +1378,70 @@
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5">
-        <v>2</v>
-      </c>
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="8"/>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" ht="57" customHeight="1" spans="1:5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="D13" s="13" t="s">
-        <v>17</v>
+      <c r="D13" s="14" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="97" orientation="landscape"/>
